--- a/artfynd/A 38752-2025 artfynd.xlsx
+++ b/artfynd/A 38752-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>59642943</v>
       </c>
       <c r="B2" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>382127.0572311731</v>
+        <v>382127</v>
       </c>
       <c r="R2" t="n">
-        <v>6245959.378122474</v>
+        <v>6245959</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +740,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>M-Äng-0148</t>
+          <t>Arkiv-M-Äng-0031</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -753,19 +748,9 @@
           <t>1996-06-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1996-06-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -800,7 +785,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>
